--- a/output7/【河洛文讀注音-閩拼調號】《相󠇡見歡󠇡·無󠇡言獨上西樓󠇡》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調號】《相󠇡見歡󠇡·無󠇡言獨上西樓󠇡》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCB088B-DA74-4908-ABF2-EE2E0E2D53E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4710B641-26A5-45CE-96ED-917BDBDF21B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-75" windowWidth="25815" windowHeight="15585" tabRatio="718" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -7272,7 +7272,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7480,6 +7480,18 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="7" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
@@ -7494,44 +7506,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="3" xfId="5" applyFill="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="6" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="8" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -10019,7 +9993,7 @@
       <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
       <c r="T3" s="16"/>
-      <c r="V3" s="68" t="s">
+      <c r="V3" s="72" t="s">
         <v>66</v>
       </c>
     </row>
@@ -10067,7 +10041,7 @@
       </c>
       <c r="R4" s="18"/>
       <c r="S4" s="19"/>
-      <c r="V4" s="71"/>
+      <c r="V4" s="75"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="20">
@@ -10119,7 +10093,7 @@
         <v>30</v>
       </c>
       <c r="S5" s="21"/>
-      <c r="V5" s="71"/>
+      <c r="V5" s="75"/>
     </row>
     <row r="6" spans="1:22" s="26" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="22"/>
@@ -10166,7 +10140,7 @@
       </c>
       <c r="R6" s="24"/>
       <c r="S6" s="25"/>
-      <c r="V6" s="71"/>
+      <c r="V6" s="75"/>
     </row>
     <row r="7" spans="1:22" s="30" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="27"/>
@@ -10187,7 +10161,7 @@
       <c r="Q7" s="14"/>
       <c r="R7" s="14"/>
       <c r="S7" s="29"/>
-      <c r="V7" s="71"/>
+      <c r="V7" s="75"/>
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="17"/>
@@ -10231,7 +10205,7 @@
         <v>553</v>
       </c>
       <c r="S8" s="19"/>
-      <c r="V8" s="71"/>
+      <c r="V8" s="75"/>
     </row>
     <row r="9" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="20">
@@ -10285,7 +10259,7 @@
       </c>
       <c r="S9" s="21"/>
       <c r="T9" s="16"/>
-      <c r="V9" s="71"/>
+      <c r="V9" s="75"/>
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="22"/>
@@ -10329,7 +10303,7 @@
         <v>554</v>
       </c>
       <c r="S10" s="31"/>
-      <c r="V10" s="71"/>
+      <c r="V10" s="75"/>
     </row>
     <row r="11" spans="1:22" s="29" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="32"/>
@@ -10349,7 +10323,7 @@
       <c r="P11" s="14"/>
       <c r="Q11" s="14"/>
       <c r="R11" s="14"/>
-      <c r="V11" s="71"/>
+      <c r="V11" s="75"/>
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="17"/>
@@ -10395,7 +10369,7 @@
         <v>579</v>
       </c>
       <c r="S12" s="19"/>
-      <c r="V12" s="71"/>
+      <c r="V12" s="75"/>
     </row>
     <row r="13" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="20">
@@ -10448,7 +10422,7 @@
         <v>99</v>
       </c>
       <c r="S13" s="21"/>
-      <c r="V13" s="71"/>
+      <c r="V13" s="75"/>
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="22"/>
@@ -10494,7 +10468,7 @@
         <v>580</v>
       </c>
       <c r="S14" s="31"/>
-      <c r="V14" s="71"/>
+      <c r="V14" s="75"/>
     </row>
     <row r="15" spans="1:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="12"/>
@@ -10514,7 +10488,7 @@
       <c r="P15" s="14"/>
       <c r="Q15" s="14"/>
       <c r="R15" s="14"/>
-      <c r="V15" s="71"/>
+      <c r="V15" s="75"/>
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="17"/>
@@ -10560,7 +10534,7 @@
       </c>
       <c r="R16" s="18"/>
       <c r="S16" s="19"/>
-      <c r="V16" s="71"/>
+      <c r="V16" s="75"/>
     </row>
     <row r="17" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="20">
@@ -10613,7 +10587,7 @@
         <v>30</v>
       </c>
       <c r="S17" s="21"/>
-      <c r="V17" s="71"/>
+      <c r="V17" s="75"/>
     </row>
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="22"/>
@@ -10659,7 +10633,7 @@
       </c>
       <c r="R18" s="24"/>
       <c r="S18" s="31"/>
-      <c r="V18" s="71"/>
+      <c r="V18" s="75"/>
     </row>
     <row r="19" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="12"/>
@@ -10679,7 +10653,7 @@
       <c r="P19" s="14"/>
       <c r="Q19" s="14"/>
       <c r="R19" s="14"/>
-      <c r="V19" s="71"/>
+      <c r="V19" s="75"/>
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="17"/>
@@ -10699,7 +10673,7 @@
       <c r="Q20" s="18"/>
       <c r="R20" s="18"/>
       <c r="S20" s="19"/>
-      <c r="V20" s="71"/>
+      <c r="V20" s="75"/>
     </row>
     <row r="21" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="20">
@@ -10726,7 +10700,7 @@
       <c r="Q21" s="41"/>
       <c r="R21" s="41"/>
       <c r="S21" s="21"/>
-      <c r="V21" s="71"/>
+      <c r="V21" s="75"/>
     </row>
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="22"/>
@@ -10746,7 +10720,7 @@
       <c r="Q22" s="24"/>
       <c r="R22" s="24"/>
       <c r="S22" s="31"/>
-      <c r="V22" s="72"/>
+      <c r="V22" s="76"/>
     </row>
     <row r="23" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="12"/>
@@ -17293,43 +17267,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:R11">
-    <cfRule type="expression" dxfId="43" priority="39">
+    <cfRule type="expression" dxfId="43" priority="40">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="39">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="40">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="expression" dxfId="41" priority="37">
+    <cfRule type="expression" dxfId="41" priority="38">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="37">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="38">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:R19">
-    <cfRule type="expression" dxfId="39" priority="35">
+    <cfRule type="expression" dxfId="39" priority="36">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="35">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="36">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D23:R23 D39:R39 D87:R87 D91:R91 D95:R95 D99:R99 D103:R103 D111:R111 D115:R115 D119:R119 D123:R123 D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
-    <cfRule type="expression" dxfId="37" priority="47">
+    <cfRule type="expression" dxfId="37" priority="48">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="47">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="48">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:R27">
-    <cfRule type="expression" dxfId="35" priority="33">
+    <cfRule type="expression" dxfId="35" priority="34">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="33">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:R31">
@@ -17341,19 +17315,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:R35">
-    <cfRule type="expression" dxfId="31" priority="29">
+    <cfRule type="expression" dxfId="31" priority="30">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="29">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:R43">
-    <cfRule type="expression" dxfId="29" priority="27">
+    <cfRule type="expression" dxfId="29" priority="28">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="27">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="28">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:R47">
@@ -17365,19 +17339,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D51:R51">
-    <cfRule type="expression" dxfId="25" priority="23">
+    <cfRule type="expression" dxfId="25" priority="24">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="23">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="24">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:R55">
-    <cfRule type="expression" dxfId="23" priority="21">
+    <cfRule type="expression" dxfId="23" priority="22">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="21">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:R59">
@@ -17389,35 +17363,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:R63">
-    <cfRule type="expression" dxfId="19" priority="17">
+    <cfRule type="expression" dxfId="19" priority="18">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:R67">
-    <cfRule type="expression" dxfId="17" priority="15">
+    <cfRule type="expression" dxfId="17" priority="16">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="15">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="16">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D71:R71">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="15" priority="14">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="13">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:R75">
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="13" priority="12">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="11">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D79:R79">
@@ -17429,11 +17403,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:R83">
-    <cfRule type="expression" dxfId="9" priority="7">
+    <cfRule type="expression" dxfId="9" priority="8">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:R107">
@@ -22502,244 +22476,244 @@
     <row r="3" spans="1:22" s="15" customFormat="1" ht="60" customHeight="1">
       <c r="B3" s="12"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="78"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="68"/>
       <c r="T3" s="16"/>
-      <c r="V3" s="68" t="s">
+      <c r="V3" s="72" t="s">
         <v>1951</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="17"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75" t="s">
+      <c r="D4" s="62"/>
+      <c r="E4" s="62" t="s">
         <v>1970</v>
       </c>
-      <c r="F4" s="75" t="s">
+      <c r="F4" s="62" t="s">
         <v>1971</v>
       </c>
-      <c r="G4" s="75" t="s">
+      <c r="G4" s="62" t="s">
         <v>1973</v>
       </c>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75" t="s">
+      <c r="H4" s="62"/>
+      <c r="I4" s="62" t="s">
         <v>635</v>
       </c>
-      <c r="J4" s="75" t="s">
+      <c r="J4" s="62" t="s">
         <v>1972</v>
       </c>
-      <c r="K4" s="75" t="s">
+      <c r="K4" s="62" t="s">
         <v>1976</v>
       </c>
-      <c r="L4" s="75" t="s">
+      <c r="L4" s="62" t="s">
         <v>587</v>
       </c>
-      <c r="M4" s="75" t="s">
+      <c r="M4" s="62" t="s">
         <v>1979</v>
       </c>
-      <c r="N4" s="75" t="s">
+      <c r="N4" s="62" t="s">
         <v>1980</v>
       </c>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="79"/>
-      <c r="V4" s="69"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="19"/>
+      <c r="V4" s="73"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="20">
         <v>1</v>
       </c>
-      <c r="D5" s="73" t="s">
+      <c r="D5" s="63" t="s">
         <v>1405</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="63" t="s">
         <v>1188</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="63" t="s">
         <v>1535</v>
       </c>
-      <c r="G5" s="73" t="s">
+      <c r="G5" s="63" t="s">
         <v>1930</v>
       </c>
-      <c r="H5" s="73" t="s">
+      <c r="H5" s="63" t="s">
         <v>1931</v>
       </c>
-      <c r="I5" s="73" t="s">
+      <c r="I5" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="73" t="s">
+      <c r="J5" s="63" t="s">
         <v>1916</v>
       </c>
-      <c r="K5" s="73" t="s">
+      <c r="K5" s="63" t="s">
         <v>1197</v>
       </c>
-      <c r="L5" s="73" t="s">
+      <c r="L5" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="73" t="s">
+      <c r="M5" s="63" t="s">
         <v>1932</v>
       </c>
-      <c r="N5" s="73" t="s">
+      <c r="N5" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="O5" s="73" t="s">
+      <c r="O5" s="63" t="s">
         <v>1406</v>
       </c>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="73"/>
-      <c r="S5" s="77"/>
-      <c r="V5" s="69"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="63"/>
+      <c r="S5" s="21"/>
+      <c r="V5" s="73"/>
     </row>
     <row r="6" spans="1:22" s="26" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="22"/>
       <c r="C6" s="23"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75" t="s">
+      <c r="D6" s="62"/>
+      <c r="E6" s="62" t="s">
         <v>1970</v>
       </c>
-      <c r="F6" s="75" t="s">
+      <c r="F6" s="62" t="s">
         <v>1972</v>
       </c>
-      <c r="G6" s="75" t="s">
+      <c r="G6" s="62" t="s">
         <v>1973</v>
       </c>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75" t="s">
+      <c r="H6" s="62"/>
+      <c r="I6" s="62" t="s">
         <v>1974</v>
       </c>
-      <c r="J6" s="75" t="s">
+      <c r="J6" s="62" t="s">
         <v>1975</v>
       </c>
-      <c r="K6" s="75" t="s">
+      <c r="K6" s="62" t="s">
         <v>1977</v>
       </c>
-      <c r="L6" s="75" t="s">
+      <c r="L6" s="62" t="s">
         <v>1978</v>
       </c>
-      <c r="M6" s="75" t="s">
+      <c r="M6" s="62" t="s">
         <v>1979</v>
       </c>
-      <c r="N6" s="76" t="s">
+      <c r="N6" s="64" t="s">
         <v>1981</v>
       </c>
-      <c r="O6" s="75"/>
-      <c r="P6" s="75"/>
-      <c r="Q6" s="76"/>
-      <c r="R6" s="76"/>
-      <c r="S6" s="80"/>
-      <c r="V6" s="69"/>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="25"/>
+      <c r="V6" s="73"/>
     </row>
     <row r="7" spans="1:22" s="30" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="27"/>
       <c r="C7" s="28"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
-      <c r="N7" s="74"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="74"/>
-      <c r="Q7" s="74"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="61"/>
+      <c r="M7" s="61"/>
+      <c r="N7" s="61"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
       <c r="R7" s="61"/>
       <c r="S7" s="29"/>
-      <c r="V7" s="69"/>
+      <c r="V7" s="73"/>
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="17"/>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="62" t="s">
         <v>1982</v>
       </c>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="62" t="s">
         <v>655</v>
       </c>
-      <c r="F8" s="75" t="s">
+      <c r="F8" s="62" t="s">
         <v>1985</v>
       </c>
-      <c r="G8" s="75" t="s">
+      <c r="G8" s="62" t="s">
         <v>760</v>
       </c>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75" t="s">
+      <c r="H8" s="62"/>
+      <c r="I8" s="62" t="s">
         <v>730</v>
       </c>
-      <c r="J8" s="75" t="s">
+      <c r="J8" s="62" t="s">
         <v>1398</v>
       </c>
-      <c r="K8" s="75"/>
-      <c r="L8" s="75"/>
-      <c r="M8" s="75"/>
-      <c r="N8" s="75"/>
-      <c r="O8" s="75"/>
-      <c r="P8" s="75"/>
-      <c r="Q8" s="75"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="62"/>
+      <c r="M8" s="62"/>
+      <c r="N8" s="62"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="62"/>
+      <c r="Q8" s="62"/>
       <c r="R8" s="62"/>
       <c r="S8" s="19"/>
-      <c r="V8" s="69"/>
+      <c r="V8" s="73"/>
     </row>
     <row r="9" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="20">
         <f>B5+1</f>
         <v>2</v>
       </c>
-      <c r="D9" s="73" t="s">
+      <c r="D9" s="63" t="s">
         <v>1388</v>
       </c>
-      <c r="E9" s="73" t="s">
+      <c r="E9" s="63" t="s">
         <v>1434</v>
       </c>
-      <c r="F9" s="73" t="s">
+      <c r="F9" s="63" t="s">
         <v>1914</v>
       </c>
-      <c r="G9" s="73" t="s">
+      <c r="G9" s="63" t="s">
         <v>200</v>
       </c>
-      <c r="H9" s="73" t="s">
+      <c r="H9" s="63" t="s">
         <v>289</v>
       </c>
-      <c r="I9" s="73" t="s">
+      <c r="I9" s="63" t="s">
         <v>1933</v>
       </c>
-      <c r="J9" s="73" t="s">
+      <c r="J9" s="63" t="s">
         <v>1934</v>
       </c>
-      <c r="K9" s="73" t="str">
+      <c r="K9" s="63" t="str">
         <f xml:space="preserve"> CHAR(10)</f>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="L9" s="73" t="str">
+      <c r="L9" s="63" t="str">
         <f xml:space="preserve"> CHAR(10)</f>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="M9" s="73"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="73" t="str">
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="63"/>
+      <c r="P9" s="63"/>
+      <c r="Q9" s="63" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -22747,287 +22721,287 @@
       <c r="R9" s="63"/>
       <c r="S9" s="21"/>
       <c r="T9" s="16"/>
-      <c r="V9" s="69"/>
+      <c r="V9" s="73"/>
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="22"/>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="64" t="s">
         <v>1983</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="64" t="s">
         <v>1984</v>
       </c>
-      <c r="F10" s="76" t="s">
+      <c r="F10" s="64" t="s">
         <v>1985</v>
       </c>
-      <c r="G10" s="76" t="s">
+      <c r="G10" s="64" t="s">
         <v>1986</v>
       </c>
-      <c r="H10" s="76"/>
-      <c r="I10" s="76" t="s">
+      <c r="H10" s="64"/>
+      <c r="I10" s="64" t="s">
         <v>1987</v>
       </c>
-      <c r="J10" s="76" t="s">
+      <c r="J10" s="64" t="s">
         <v>1918</v>
       </c>
-      <c r="K10" s="76"/>
-      <c r="L10" s="76"/>
-      <c r="M10" s="76"/>
-      <c r="N10" s="76"/>
-      <c r="O10" s="76"/>
-      <c r="P10" s="76"/>
-      <c r="Q10" s="76"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="64"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
       <c r="R10" s="64"/>
       <c r="S10" s="31"/>
-      <c r="V10" s="69"/>
+      <c r="V10" s="73"/>
     </row>
     <row r="11" spans="1:22" s="29" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="32"/>
       <c r="C11" s="33"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="74"/>
-      <c r="K11" s="74"/>
-      <c r="L11" s="74"/>
-      <c r="M11" s="74"/>
-      <c r="N11" s="74"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="74"/>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="74"/>
-      <c r="S11" s="81"/>
-      <c r="V11" s="69"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="61"/>
+      <c r="M11" s="61"/>
+      <c r="N11" s="61"/>
+      <c r="O11" s="61"/>
+      <c r="P11" s="61"/>
+      <c r="Q11" s="61"/>
+      <c r="R11" s="61"/>
+      <c r="S11" s="69"/>
+      <c r="V11" s="73"/>
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="17"/>
-      <c r="D12" s="75" t="s">
+      <c r="D12" s="62" t="s">
         <v>635</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="62" t="s">
         <v>1972</v>
       </c>
-      <c r="F12" s="75" t="s">
+      <c r="F12" s="62" t="s">
         <v>1976</v>
       </c>
-      <c r="G12" s="75" t="s">
+      <c r="G12" s="62" t="s">
         <v>587</v>
       </c>
-      <c r="H12" s="75" t="s">
+      <c r="H12" s="62" t="s">
         <v>1979</v>
       </c>
-      <c r="I12" s="75" t="s">
+      <c r="I12" s="62" t="s">
         <v>1980</v>
       </c>
-      <c r="J12" s="75"/>
-      <c r="K12" s="75" t="s">
+      <c r="J12" s="62"/>
+      <c r="K12" s="62" t="s">
         <v>1988</v>
       </c>
-      <c r="L12" s="75" t="s">
+      <c r="L12" s="62" t="s">
         <v>1990</v>
       </c>
-      <c r="M12" s="75" t="s">
+      <c r="M12" s="62" t="s">
         <v>1992</v>
       </c>
-      <c r="N12" s="75"/>
-      <c r="O12" s="75" t="s">
+      <c r="N12" s="62"/>
+      <c r="O12" s="62" t="s">
         <v>810</v>
       </c>
-      <c r="P12" s="75" t="s">
+      <c r="P12" s="62" t="s">
         <v>774</v>
       </c>
-      <c r="Q12" s="75" t="s">
+      <c r="Q12" s="62" t="s">
         <v>914</v>
       </c>
-      <c r="R12" s="75" t="s">
+      <c r="R12" s="62" t="s">
         <v>888</v>
       </c>
-      <c r="S12" s="79"/>
-      <c r="V12" s="69"/>
+      <c r="S12" s="19"/>
+      <c r="V12" s="73"/>
     </row>
     <row r="13" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="20">
         <f>B9+1</f>
         <v>3</v>
       </c>
-      <c r="D13" s="73" t="s">
+      <c r="D13" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="73" t="s">
+      <c r="E13" s="63" t="s">
         <v>1916</v>
       </c>
-      <c r="F13" s="73" t="s">
+      <c r="F13" s="63" t="s">
         <v>1197</v>
       </c>
-      <c r="G13" s="73" t="s">
+      <c r="G13" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="73" t="s">
+      <c r="H13" s="63" t="s">
         <v>1932</v>
       </c>
-      <c r="I13" s="73" t="s">
+      <c r="I13" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="73" t="s">
+      <c r="J13" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="K13" s="73" t="s">
+      <c r="K13" s="63" t="s">
         <v>167</v>
       </c>
-      <c r="L13" s="73" t="s">
+      <c r="L13" s="63" t="s">
         <v>1913</v>
       </c>
-      <c r="M13" s="73" t="s">
+      <c r="M13" s="63" t="s">
         <v>1935</v>
       </c>
-      <c r="N13" s="73" t="s">
+      <c r="N13" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="O13" s="73" t="s">
+      <c r="O13" s="63" t="s">
         <v>1936</v>
       </c>
-      <c r="P13" s="73" t="s">
+      <c r="P13" s="63" t="s">
         <v>1937</v>
       </c>
-      <c r="Q13" s="73" t="s">
+      <c r="Q13" s="63" t="s">
         <v>1938</v>
       </c>
-      <c r="R13" s="73" t="s">
+      <c r="R13" s="63" t="s">
         <v>1939</v>
       </c>
-      <c r="S13" s="77"/>
-      <c r="V13" s="69"/>
+      <c r="S13" s="21"/>
+      <c r="V13" s="73"/>
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="22"/>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="64" t="s">
         <v>1974</v>
       </c>
-      <c r="E14" s="76" t="s">
+      <c r="E14" s="64" t="s">
         <v>1975</v>
       </c>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="64" t="s">
         <v>1977</v>
       </c>
-      <c r="G14" s="76" t="s">
+      <c r="G14" s="64" t="s">
         <v>1978</v>
       </c>
-      <c r="H14" s="76" t="s">
+      <c r="H14" s="64" t="s">
         <v>1979</v>
       </c>
-      <c r="I14" s="76" t="s">
+      <c r="I14" s="64" t="s">
         <v>1981</v>
       </c>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76" t="s">
+      <c r="J14" s="64"/>
+      <c r="K14" s="64" t="s">
         <v>1989</v>
       </c>
-      <c r="L14" s="76" t="s">
+      <c r="L14" s="64" t="s">
         <v>1991</v>
       </c>
-      <c r="M14" s="76" t="s">
+      <c r="M14" s="64" t="s">
         <v>1993</v>
       </c>
-      <c r="N14" s="76"/>
-      <c r="O14" s="76" t="s">
+      <c r="N14" s="64"/>
+      <c r="O14" s="64" t="s">
         <v>810</v>
       </c>
-      <c r="P14" s="76" t="s">
+      <c r="P14" s="64" t="s">
         <v>1994</v>
       </c>
-      <c r="Q14" s="76" t="s">
+      <c r="Q14" s="64" t="s">
         <v>2043</v>
       </c>
-      <c r="R14" s="76" t="s">
+      <c r="R14" s="64" t="s">
         <v>1995</v>
       </c>
-      <c r="S14" s="82"/>
-      <c r="V14" s="69"/>
+      <c r="S14" s="31"/>
+      <c r="V14" s="73"/>
     </row>
     <row r="15" spans="1:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="12"/>
       <c r="C15" s="34"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="74"/>
-      <c r="M15" s="74"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="61"/>
+      <c r="M15" s="61"/>
       <c r="N15" s="61"/>
       <c r="O15" s="61"/>
       <c r="P15" s="61"/>
       <c r="Q15" s="61"/>
       <c r="R15" s="61"/>
-      <c r="V15" s="69"/>
+      <c r="V15" s="73"/>
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="17"/>
-      <c r="D16" s="75" t="s">
+      <c r="D16" s="62" t="s">
         <v>1996</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="62" t="s">
         <v>1997</v>
       </c>
-      <c r="F16" s="75" t="s">
+      <c r="F16" s="62" t="s">
         <v>1999</v>
       </c>
-      <c r="G16" s="75" t="s">
+      <c r="G16" s="62" t="s">
         <v>2001</v>
       </c>
-      <c r="H16" s="75" t="s">
+      <c r="H16" s="62" t="s">
         <v>2002</v>
       </c>
-      <c r="I16" s="75"/>
-      <c r="J16" s="75"/>
-      <c r="K16" s="75"/>
-      <c r="L16" s="75"/>
-      <c r="M16" s="75"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="62"/>
+      <c r="M16" s="62"/>
       <c r="N16" s="62"/>
       <c r="O16" s="62"/>
       <c r="P16" s="62"/>
       <c r="Q16" s="62"/>
       <c r="R16" s="62"/>
       <c r="S16" s="19"/>
-      <c r="V16" s="69"/>
+      <c r="V16" s="73"/>
     </row>
     <row r="17" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="20">
         <f>B13+1</f>
         <v>4</v>
       </c>
-      <c r="D17" s="73" t="s">
+      <c r="D17" s="63" t="s">
         <v>1443</v>
       </c>
-      <c r="E17" s="73" t="s">
+      <c r="E17" s="63" t="s">
         <v>1940</v>
       </c>
-      <c r="F17" s="73" t="s">
+      <c r="F17" s="63" t="s">
         <v>1941</v>
       </c>
-      <c r="G17" s="73" t="s">
+      <c r="G17" s="63" t="s">
         <v>1942</v>
       </c>
-      <c r="H17" s="73" t="s">
+      <c r="H17" s="63" t="s">
         <v>1943</v>
       </c>
-      <c r="I17" s="73" t="s">
+      <c r="I17" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="J17" s="73" t="str">
+      <c r="J17" s="63" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="K17" s="73"/>
-      <c r="L17" s="73"/>
-      <c r="M17" s="73" t="str">
+      <c r="K17" s="63"/>
+      <c r="L17" s="63"/>
+      <c r="M17" s="63" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -23038,280 +23012,280 @@
       <c r="Q17" s="63"/>
       <c r="R17" s="63"/>
       <c r="S17" s="21"/>
-      <c r="V17" s="69"/>
+      <c r="V17" s="73"/>
     </row>
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="22"/>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="64" t="s">
         <v>1996</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="64" t="s">
         <v>1998</v>
       </c>
-      <c r="F18" s="76" t="s">
+      <c r="F18" s="64" t="s">
         <v>2000</v>
       </c>
-      <c r="G18" s="76" t="s">
+      <c r="G18" s="64" t="s">
         <v>2001</v>
       </c>
-      <c r="H18" s="76" t="s">
+      <c r="H18" s="64" t="s">
         <v>2002</v>
       </c>
-      <c r="I18" s="76"/>
-      <c r="J18" s="76"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="76"/>
-      <c r="M18" s="76"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
       <c r="N18" s="64"/>
       <c r="O18" s="64"/>
       <c r="P18" s="64"/>
       <c r="Q18" s="64"/>
       <c r="R18" s="64"/>
       <c r="S18" s="31"/>
-      <c r="V18" s="69"/>
+      <c r="V18" s="73"/>
     </row>
     <row r="19" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="12"/>
       <c r="C19" s="34"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="74"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="74"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="74"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="74"/>
-      <c r="S19" s="84"/>
-      <c r="V19" s="69"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="61"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="61"/>
+      <c r="R19" s="61"/>
+      <c r="S19" s="71"/>
+      <c r="V19" s="73"/>
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="17"/>
-      <c r="D20" s="75" t="s">
+      <c r="D20" s="62" t="s">
         <v>2003</v>
       </c>
-      <c r="E20" s="75" t="s">
+      <c r="E20" s="62" t="s">
         <v>704</v>
       </c>
-      <c r="F20" s="75" t="s">
+      <c r="F20" s="62" t="s">
         <v>2006</v>
       </c>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75" t="s">
+      <c r="G20" s="62"/>
+      <c r="H20" s="62" t="s">
         <v>730</v>
       </c>
-      <c r="I20" s="75" t="s">
+      <c r="I20" s="62" t="s">
         <v>2008</v>
       </c>
-      <c r="J20" s="75" t="s">
+      <c r="J20" s="62" t="s">
         <v>2010</v>
       </c>
-      <c r="K20" s="75"/>
-      <c r="L20" s="75" t="s">
+      <c r="K20" s="62"/>
+      <c r="L20" s="62" t="s">
         <v>896</v>
       </c>
-      <c r="M20" s="75" t="s">
+      <c r="M20" s="62" t="s">
         <v>2013</v>
       </c>
-      <c r="N20" s="75" t="s">
+      <c r="N20" s="62" t="s">
         <v>2015</v>
       </c>
-      <c r="O20" s="75"/>
-      <c r="P20" s="75"/>
-      <c r="Q20" s="75"/>
-      <c r="R20" s="75"/>
-      <c r="S20" s="79"/>
-      <c r="V20" s="69"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="62"/>
+      <c r="S20" s="19"/>
+      <c r="V20" s="73"/>
     </row>
     <row r="21" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="20">
         <f>B17+1</f>
         <v>5</v>
       </c>
-      <c r="D21" s="73" t="s">
+      <c r="D21" s="63" t="s">
         <v>1944</v>
       </c>
-      <c r="E21" s="73" t="s">
+      <c r="E21" s="63" t="s">
         <v>168</v>
       </c>
-      <c r="F21" s="73" t="s">
+      <c r="F21" s="63" t="s">
         <v>1917</v>
       </c>
-      <c r="G21" s="83" t="s">
+      <c r="G21" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="73" t="s">
+      <c r="H21" s="63" t="s">
         <v>1589</v>
       </c>
-      <c r="I21" s="73" t="s">
+      <c r="I21" s="63" t="s">
         <v>1945</v>
       </c>
-      <c r="J21" s="73" t="s">
+      <c r="J21" s="63" t="s">
         <v>1458</v>
       </c>
-      <c r="K21" s="73" t="s">
+      <c r="K21" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="73" t="s">
+      <c r="L21" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="M21" s="73" t="s">
+      <c r="M21" s="63" t="s">
         <v>1946</v>
       </c>
-      <c r="N21" s="73" t="s">
+      <c r="N21" s="63" t="s">
         <v>1947</v>
       </c>
-      <c r="O21" s="73" t="s">
+      <c r="O21" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="P21" s="73" t="str">
+      <c r="P21" s="63" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="Q21" s="73"/>
-      <c r="R21" s="73"/>
-      <c r="S21" s="77"/>
-      <c r="V21" s="69"/>
+      <c r="Q21" s="63"/>
+      <c r="R21" s="63"/>
+      <c r="S21" s="21"/>
+      <c r="V21" s="73"/>
     </row>
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="22"/>
-      <c r="D22" s="76" t="s">
+      <c r="D22" s="64" t="s">
         <v>2004</v>
       </c>
-      <c r="E22" s="76" t="s">
+      <c r="E22" s="64" t="s">
         <v>2005</v>
       </c>
-      <c r="F22" s="76" t="s">
+      <c r="F22" s="64" t="s">
         <v>2007</v>
       </c>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76" t="s">
+      <c r="G22" s="64"/>
+      <c r="H22" s="64" t="s">
         <v>1987</v>
       </c>
-      <c r="I22" s="76" t="s">
+      <c r="I22" s="64" t="s">
         <v>2009</v>
       </c>
-      <c r="J22" s="76" t="s">
+      <c r="J22" s="64" t="s">
         <v>2011</v>
       </c>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76" t="s">
+      <c r="K22" s="64"/>
+      <c r="L22" s="64" t="s">
         <v>2012</v>
       </c>
-      <c r="M22" s="76" t="s">
+      <c r="M22" s="64" t="s">
         <v>2014</v>
       </c>
-      <c r="N22" s="76" t="s">
+      <c r="N22" s="64" t="s">
         <v>2016</v>
       </c>
-      <c r="O22" s="76"/>
-      <c r="P22" s="76"/>
-      <c r="Q22" s="76"/>
-      <c r="R22" s="76"/>
-      <c r="S22" s="82"/>
-      <c r="V22" s="69"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="64"/>
+      <c r="R22" s="64"/>
+      <c r="S22" s="31"/>
+      <c r="V22" s="73"/>
     </row>
     <row r="23" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="12"/>
       <c r="C23" s="34"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74"/>
-      <c r="J23" s="74"/>
-      <c r="K23" s="74"/>
-      <c r="L23" s="74"/>
-      <c r="M23" s="74"/>
-      <c r="N23" s="74"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="61"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="61"/>
       <c r="O23" s="61"/>
       <c r="P23" s="61"/>
       <c r="Q23" s="61"/>
       <c r="R23" s="61"/>
-      <c r="V23" s="69"/>
+      <c r="V23" s="73"/>
     </row>
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="17"/>
-      <c r="D24" s="75" t="s">
+      <c r="D24" s="62" t="s">
         <v>2017</v>
       </c>
-      <c r="E24" s="75" t="s">
+      <c r="E24" s="62" t="s">
         <v>896</v>
       </c>
-      <c r="F24" s="75" t="s">
+      <c r="F24" s="62" t="s">
         <v>617</v>
       </c>
-      <c r="G24" s="75" t="s">
+      <c r="G24" s="62" t="s">
         <v>2020</v>
       </c>
-      <c r="H24" s="75" t="s">
+      <c r="H24" s="62" t="s">
         <v>2022</v>
       </c>
-      <c r="I24" s="75" t="s">
+      <c r="I24" s="62" t="s">
         <v>2023</v>
       </c>
-      <c r="J24" s="75" t="s">
+      <c r="J24" s="62" t="s">
         <v>611</v>
       </c>
-      <c r="K24" s="75" t="s">
+      <c r="K24" s="62" t="s">
         <v>846</v>
       </c>
-      <c r="L24" s="75" t="s">
+      <c r="L24" s="62" t="s">
         <v>2044</v>
       </c>
-      <c r="M24" s="75"/>
-      <c r="N24" s="75"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="62"/>
       <c r="O24" s="62"/>
       <c r="P24" s="62"/>
       <c r="Q24" s="62"/>
       <c r="R24" s="62"/>
       <c r="S24" s="19"/>
-      <c r="V24" s="69"/>
+      <c r="V24" s="73"/>
     </row>
     <row r="25" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B25" s="20">
         <f>B21+1</f>
         <v>6</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="D25" s="63" t="s">
         <v>1948</v>
       </c>
-      <c r="E25" s="73" t="s">
+      <c r="E25" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="73" t="s">
+      <c r="F25" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="G25" s="73" t="s">
+      <c r="G25" s="63" t="s">
         <v>1949</v>
       </c>
-      <c r="H25" s="73" t="s">
+      <c r="H25" s="63" t="s">
         <v>1950</v>
       </c>
-      <c r="I25" s="73" t="s">
+      <c r="I25" s="63" t="s">
         <v>1915</v>
       </c>
-      <c r="J25" s="73" t="s">
+      <c r="J25" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="K25" s="73" t="s">
+      <c r="K25" s="63" t="s">
         <v>253</v>
       </c>
-      <c r="L25" s="73" t="s">
+      <c r="L25" s="63" t="s">
         <v>1198</v>
       </c>
-      <c r="M25" s="73" t="s">
+      <c r="M25" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="N25" s="73" t="str">
+      <c r="N25" s="63" t="str">
         <f>CHAR(10)</f>
         <v xml:space="preserve">
 </v>
@@ -23321,50 +23295,50 @@
       <c r="Q25" s="63"/>
       <c r="R25" s="63"/>
       <c r="S25" s="21"/>
-      <c r="V25" s="69"/>
+      <c r="V25" s="73"/>
     </row>
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="22"/>
-      <c r="D26" s="76" t="s">
+      <c r="D26" s="64" t="s">
         <v>2018</v>
       </c>
-      <c r="E26" s="76" t="s">
+      <c r="E26" s="64" t="s">
         <v>2012</v>
       </c>
-      <c r="F26" s="76" t="s">
+      <c r="F26" s="64" t="s">
         <v>2019</v>
       </c>
-      <c r="G26" s="76" t="s">
+      <c r="G26" s="64" t="s">
         <v>2021</v>
       </c>
-      <c r="H26" s="76" t="s">
+      <c r="H26" s="64" t="s">
         <v>2022</v>
       </c>
-      <c r="I26" s="76" t="s">
+      <c r="I26" s="64" t="s">
         <v>2024</v>
       </c>
-      <c r="J26" s="76" t="s">
+      <c r="J26" s="64" t="s">
         <v>2025</v>
       </c>
-      <c r="K26" s="76" t="s">
+      <c r="K26" s="64" t="s">
         <v>846</v>
       </c>
-      <c r="L26" s="76" t="s">
+      <c r="L26" s="64" t="s">
         <v>2045</v>
       </c>
-      <c r="M26" s="76"/>
-      <c r="N26" s="76"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="64"/>
       <c r="O26" s="64"/>
       <c r="P26" s="64"/>
       <c r="Q26" s="64"/>
       <c r="R26" s="64"/>
       <c r="S26" s="31"/>
-      <c r="V26" s="69"/>
+      <c r="V26" s="73"/>
     </row>
     <row r="27" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B27" s="12"/>
       <c r="C27" s="34"/>
-      <c r="D27" s="74"/>
+      <c r="D27" s="61"/>
       <c r="E27" s="61"/>
       <c r="F27" s="61"/>
       <c r="G27" s="61"/>
@@ -23383,11 +23357,11 @@
         <f t="shared" ref="U27:U32" si="1" xml:space="preserve"> MID($N$26,4,1)</f>
         <v/>
       </c>
-      <c r="V27" s="69"/>
+      <c r="V27" s="73"/>
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="17"/>
-      <c r="D28" s="75"/>
+      <c r="D28" s="62"/>
       <c r="E28" s="62"/>
       <c r="F28" s="62"/>
       <c r="G28" s="62"/>
@@ -23407,14 +23381,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V28" s="69"/>
+      <c r="V28" s="73"/>
     </row>
     <row r="29" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B29" s="20">
         <f>B25+1</f>
         <v>7</v>
       </c>
-      <c r="D29" s="73" t="s">
+      <c r="D29" s="63" t="s">
         <v>38</v>
       </c>
       <c r="E29" s="63"/>
@@ -23436,11 +23410,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V29" s="69"/>
+      <c r="V29" s="73"/>
     </row>
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="22"/>
-      <c r="D30" s="76"/>
+      <c r="D30" s="64"/>
       <c r="E30" s="64"/>
       <c r="F30" s="64"/>
       <c r="G30" s="64"/>
@@ -23460,12 +23434,12 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V30" s="69"/>
+      <c r="V30" s="73"/>
     </row>
     <row r="31" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B31" s="12"/>
       <c r="C31" s="34"/>
-      <c r="D31" s="74"/>
+      <c r="D31" s="61"/>
       <c r="E31" s="61"/>
       <c r="F31" s="61"/>
       <c r="G31" s="61"/>
@@ -23484,11 +23458,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V31" s="69"/>
+      <c r="V31" s="73"/>
     </row>
     <row r="32" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="17"/>
-      <c r="D32" s="75"/>
+      <c r="D32" s="62"/>
       <c r="E32" s="62"/>
       <c r="F32" s="62"/>
       <c r="G32" s="62"/>
@@ -23508,14 +23482,14 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V32" s="69"/>
+      <c r="V32" s="73"/>
     </row>
     <row r="33" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B33" s="20">
         <f>B29+1</f>
         <v>8</v>
       </c>
-      <c r="D33" s="73"/>
+      <c r="D33" s="63"/>
       <c r="E33" s="63"/>
       <c r="F33" s="63"/>
       <c r="G33" s="63"/>
@@ -23531,11 +23505,11 @@
       <c r="Q33" s="63"/>
       <c r="R33" s="63"/>
       <c r="S33" s="21"/>
-      <c r="V33" s="69"/>
+      <c r="V33" s="73"/>
     </row>
     <row r="34" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="22"/>
-      <c r="D34" s="76"/>
+      <c r="D34" s="64"/>
       <c r="E34" s="64"/>
       <c r="F34" s="64"/>
       <c r="G34" s="64"/>
@@ -23551,7 +23525,7 @@
       <c r="Q34" s="64"/>
       <c r="R34" s="64"/>
       <c r="S34" s="31"/>
-      <c r="V34" s="69"/>
+      <c r="V34" s="73"/>
     </row>
     <row r="35" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B35" s="12"/>
@@ -23571,7 +23545,7 @@
       <c r="P35" s="61"/>
       <c r="Q35" s="61"/>
       <c r="R35" s="61"/>
-      <c r="V35" s="69"/>
+      <c r="V35" s="73"/>
     </row>
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="17"/>
@@ -23591,7 +23565,7 @@
       <c r="Q36" s="62"/>
       <c r="R36" s="62"/>
       <c r="S36" s="19"/>
-      <c r="V36" s="69"/>
+      <c r="V36" s="73"/>
     </row>
     <row r="37" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B37" s="20">
@@ -23614,7 +23588,7 @@
       <c r="Q37" s="63"/>
       <c r="R37" s="63"/>
       <c r="S37" s="21"/>
-      <c r="V37" s="69"/>
+      <c r="V37" s="73"/>
     </row>
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="22"/>
@@ -23634,7 +23608,7 @@
       <c r="Q38" s="64"/>
       <c r="R38" s="64"/>
       <c r="S38" s="31"/>
-      <c r="V38" s="69"/>
+      <c r="V38" s="73"/>
     </row>
     <row r="39" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B39" s="12"/>
@@ -23654,7 +23628,7 @@
       <c r="P39" s="61"/>
       <c r="Q39" s="61"/>
       <c r="R39" s="61"/>
-      <c r="V39" s="69"/>
+      <c r="V39" s="73"/>
     </row>
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="17"/>
@@ -23674,7 +23648,7 @@
       <c r="Q40" s="62"/>
       <c r="R40" s="62"/>
       <c r="S40" s="19"/>
-      <c r="V40" s="69"/>
+      <c r="V40" s="73"/>
     </row>
     <row r="41" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B41" s="20">
@@ -23697,7 +23671,7 @@
       <c r="Q41" s="63"/>
       <c r="R41" s="63"/>
       <c r="S41" s="21"/>
-      <c r="V41" s="69"/>
+      <c r="V41" s="73"/>
     </row>
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="22"/>
@@ -23717,7 +23691,7 @@
       <c r="Q42" s="64"/>
       <c r="R42" s="64"/>
       <c r="S42" s="31"/>
-      <c r="V42" s="69"/>
+      <c r="V42" s="73"/>
     </row>
     <row r="43" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B43" s="12"/>
@@ -23737,7 +23711,7 @@
       <c r="P43" s="61"/>
       <c r="Q43" s="61"/>
       <c r="R43" s="61"/>
-      <c r="V43" s="69"/>
+      <c r="V43" s="73"/>
     </row>
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="17"/>
@@ -23757,7 +23731,7 @@
       <c r="Q44" s="62"/>
       <c r="R44" s="62"/>
       <c r="S44" s="19"/>
-      <c r="V44" s="69"/>
+      <c r="V44" s="73"/>
     </row>
     <row r="45" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B45" s="20">
@@ -23780,7 +23754,7 @@
       <c r="Q45" s="63"/>
       <c r="R45" s="63"/>
       <c r="S45" s="21"/>
-      <c r="V45" s="69"/>
+      <c r="V45" s="73"/>
     </row>
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="22"/>
@@ -23800,7 +23774,7 @@
       <c r="Q46" s="64"/>
       <c r="R46" s="64"/>
       <c r="S46" s="31"/>
-      <c r="V46" s="69"/>
+      <c r="V46" s="73"/>
     </row>
     <row r="47" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B47" s="12"/>
@@ -23808,7 +23782,7 @@
       <c r="D47" s="61"/>
       <c r="E47" s="61"/>
       <c r="F47" s="61"/>
-      <c r="G47" s="74"/>
+      <c r="G47" s="61"/>
       <c r="H47" s="61"/>
       <c r="I47" s="61"/>
       <c r="J47" s="61"/>
@@ -23820,14 +23794,14 @@
       <c r="P47" s="61"/>
       <c r="Q47" s="61"/>
       <c r="R47" s="61"/>
-      <c r="V47" s="69"/>
+      <c r="V47" s="73"/>
     </row>
     <row r="48" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="17"/>
       <c r="D48" s="62"/>
       <c r="E48" s="62"/>
       <c r="F48" s="62"/>
-      <c r="G48" s="75"/>
+      <c r="G48" s="62"/>
       <c r="H48" s="62"/>
       <c r="I48" s="62"/>
       <c r="J48" s="62"/>
@@ -23840,7 +23814,7 @@
       <c r="Q48" s="62"/>
       <c r="R48" s="62"/>
       <c r="S48" s="19"/>
-      <c r="V48" s="69"/>
+      <c r="V48" s="73"/>
     </row>
     <row r="49" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B49" s="20">
@@ -23850,7 +23824,7 @@
       <c r="D49" s="63"/>
       <c r="E49" s="63"/>
       <c r="F49" s="63"/>
-      <c r="G49" s="73"/>
+      <c r="G49" s="63"/>
       <c r="H49" s="63"/>
       <c r="I49" s="63"/>
       <c r="J49" s="63"/>
@@ -23863,14 +23837,14 @@
       <c r="Q49" s="63"/>
       <c r="R49" s="63"/>
       <c r="S49" s="21"/>
-      <c r="V49" s="69"/>
+      <c r="V49" s="73"/>
     </row>
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="22"/>
       <c r="D50" s="64"/>
       <c r="E50" s="64"/>
       <c r="F50" s="64"/>
-      <c r="G50" s="76"/>
+      <c r="G50" s="64"/>
       <c r="H50" s="64"/>
       <c r="I50" s="64"/>
       <c r="J50" s="64"/>
@@ -23883,7 +23857,7 @@
       <c r="Q50" s="64"/>
       <c r="R50" s="64"/>
       <c r="S50" s="31"/>
-      <c r="V50" s="69"/>
+      <c r="V50" s="73"/>
     </row>
     <row r="51" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B51" s="12"/>
@@ -23903,7 +23877,7 @@
       <c r="P51" s="61"/>
       <c r="Q51" s="61"/>
       <c r="R51" s="61"/>
-      <c r="V51" s="69"/>
+      <c r="V51" s="73"/>
     </row>
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="17"/>
@@ -23923,7 +23897,7 @@
       <c r="Q52" s="62"/>
       <c r="R52" s="62"/>
       <c r="S52" s="19"/>
-      <c r="V52" s="69"/>
+      <c r="V52" s="73"/>
     </row>
     <row r="53" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B53" s="20">
@@ -23946,7 +23920,7 @@
       <c r="Q53" s="63"/>
       <c r="R53" s="63"/>
       <c r="S53" s="21"/>
-      <c r="V53" s="69"/>
+      <c r="V53" s="73"/>
     </row>
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="22"/>
@@ -23966,7 +23940,7 @@
       <c r="Q54" s="64"/>
       <c r="R54" s="64"/>
       <c r="S54" s="31"/>
-      <c r="V54" s="69"/>
+      <c r="V54" s="73"/>
     </row>
     <row r="55" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B55" s="12"/>
@@ -23986,7 +23960,7 @@
       <c r="P55" s="61"/>
       <c r="Q55" s="61"/>
       <c r="R55" s="61"/>
-      <c r="V55" s="69"/>
+      <c r="V55" s="73"/>
     </row>
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="17"/>
@@ -24006,7 +23980,7 @@
       <c r="Q56" s="62"/>
       <c r="R56" s="62"/>
       <c r="S56" s="19"/>
-      <c r="V56" s="69"/>
+      <c r="V56" s="73"/>
     </row>
     <row r="57" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B57" s="20">
@@ -24029,7 +24003,7 @@
       <c r="Q57" s="63"/>
       <c r="R57" s="63"/>
       <c r="S57" s="21"/>
-      <c r="V57" s="69"/>
+      <c r="V57" s="73"/>
     </row>
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="22"/>
@@ -24049,7 +24023,7 @@
       <c r="Q58" s="64"/>
       <c r="R58" s="64"/>
       <c r="S58" s="31"/>
-      <c r="V58" s="69"/>
+      <c r="V58" s="73"/>
     </row>
     <row r="59" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B59" s="12"/>
@@ -24069,7 +24043,7 @@
       <c r="P59" s="61"/>
       <c r="Q59" s="61"/>
       <c r="R59" s="61"/>
-      <c r="V59" s="69"/>
+      <c r="V59" s="73"/>
     </row>
     <row r="60" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="17"/>
@@ -24089,7 +24063,7 @@
       <c r="Q60" s="62"/>
       <c r="R60" s="62"/>
       <c r="S60" s="19"/>
-      <c r="V60" s="69"/>
+      <c r="V60" s="73"/>
     </row>
     <row r="61" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B61" s="20">
@@ -24112,7 +24086,7 @@
       <c r="Q61" s="63"/>
       <c r="R61" s="63"/>
       <c r="S61" s="21"/>
-      <c r="V61" s="69"/>
+      <c r="V61" s="73"/>
     </row>
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="22"/>
@@ -24132,7 +24106,7 @@
       <c r="Q62" s="64"/>
       <c r="R62" s="64"/>
       <c r="S62" s="31"/>
-      <c r="V62" s="69"/>
+      <c r="V62" s="73"/>
     </row>
     <row r="63" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B63" s="12"/>
@@ -24152,7 +24126,7 @@
       <c r="P63" s="61"/>
       <c r="Q63" s="61"/>
       <c r="R63" s="61"/>
-      <c r="V63" s="69"/>
+      <c r="V63" s="73"/>
     </row>
     <row r="64" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B64" s="17"/>
@@ -24172,7 +24146,7 @@
       <c r="Q64" s="62"/>
       <c r="R64" s="62"/>
       <c r="S64" s="19"/>
-      <c r="V64" s="69"/>
+      <c r="V64" s="73"/>
     </row>
     <row r="65" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B65" s="20">
@@ -24195,7 +24169,7 @@
       <c r="Q65" s="63"/>
       <c r="R65" s="63"/>
       <c r="S65" s="21"/>
-      <c r="V65" s="69"/>
+      <c r="V65" s="73"/>
     </row>
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="22"/>
@@ -24215,7 +24189,7 @@
       <c r="Q66" s="64"/>
       <c r="R66" s="64"/>
       <c r="S66" s="31"/>
-      <c r="V66" s="69"/>
+      <c r="V66" s="73"/>
     </row>
     <row r="67" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B67" s="12"/>
@@ -24223,7 +24197,7 @@
       <c r="D67" s="61"/>
       <c r="E67" s="61"/>
       <c r="F67" s="61"/>
-      <c r="G67" s="74"/>
+      <c r="G67" s="61"/>
       <c r="H67" s="61"/>
       <c r="I67" s="61"/>
       <c r="J67" s="61"/>
@@ -24235,14 +24209,14 @@
       <c r="P67" s="61"/>
       <c r="Q67" s="61"/>
       <c r="R67" s="61"/>
-      <c r="V67" s="69"/>
+      <c r="V67" s="73"/>
     </row>
     <row r="68" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="17"/>
       <c r="D68" s="62"/>
       <c r="E68" s="62"/>
       <c r="F68" s="62"/>
-      <c r="G68" s="75"/>
+      <c r="G68" s="62"/>
       <c r="H68" s="62"/>
       <c r="I68" s="62"/>
       <c r="J68" s="62"/>
@@ -24255,7 +24229,7 @@
       <c r="Q68" s="62"/>
       <c r="R68" s="62"/>
       <c r="S68" s="19"/>
-      <c r="V68" s="69"/>
+      <c r="V68" s="73"/>
     </row>
     <row r="69" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B69" s="20">
@@ -24265,7 +24239,7 @@
       <c r="D69" s="63"/>
       <c r="E69" s="63"/>
       <c r="F69" s="63"/>
-      <c r="G69" s="73"/>
+      <c r="G69" s="63"/>
       <c r="H69" s="63"/>
       <c r="I69" s="63"/>
       <c r="J69" s="63"/>
@@ -24278,14 +24252,14 @@
       <c r="Q69" s="63"/>
       <c r="R69" s="63"/>
       <c r="S69" s="21"/>
-      <c r="V69" s="69"/>
+      <c r="V69" s="73"/>
     </row>
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="22"/>
       <c r="D70" s="64"/>
       <c r="E70" s="64"/>
       <c r="F70" s="64"/>
-      <c r="G70" s="76"/>
+      <c r="G70" s="64"/>
       <c r="H70" s="64"/>
       <c r="I70" s="64"/>
       <c r="J70" s="64"/>
@@ -24298,7 +24272,7 @@
       <c r="Q70" s="64"/>
       <c r="R70" s="64"/>
       <c r="S70" s="31"/>
-      <c r="V70" s="69"/>
+      <c r="V70" s="73"/>
     </row>
     <row r="71" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B71" s="12"/>
@@ -24318,7 +24292,7 @@
       <c r="P71" s="61"/>
       <c r="Q71" s="61"/>
       <c r="R71" s="61"/>
-      <c r="V71" s="69"/>
+      <c r="V71" s="73"/>
     </row>
     <row r="72" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="17"/>
@@ -24338,7 +24312,7 @@
       <c r="Q72" s="62"/>
       <c r="R72" s="62"/>
       <c r="S72" s="19"/>
-      <c r="V72" s="69"/>
+      <c r="V72" s="73"/>
     </row>
     <row r="73" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B73" s="20">
@@ -24361,7 +24335,7 @@
       <c r="Q73" s="63"/>
       <c r="R73" s="63"/>
       <c r="S73" s="21"/>
-      <c r="V73" s="69"/>
+      <c r="V73" s="73"/>
     </row>
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="22"/>
@@ -24381,7 +24355,7 @@
       <c r="Q74" s="64"/>
       <c r="R74" s="64"/>
       <c r="S74" s="31"/>
-      <c r="V74" s="69"/>
+      <c r="V74" s="73"/>
     </row>
     <row r="75" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B75" s="12"/>
@@ -24401,7 +24375,7 @@
       <c r="P75" s="61"/>
       <c r="Q75" s="61"/>
       <c r="R75" s="61"/>
-      <c r="V75" s="69"/>
+      <c r="V75" s="73"/>
     </row>
     <row r="76" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="17"/>
@@ -24421,7 +24395,7 @@
       <c r="Q76" s="62"/>
       <c r="R76" s="62"/>
       <c r="S76" s="19"/>
-      <c r="V76" s="69"/>
+      <c r="V76" s="73"/>
     </row>
     <row r="77" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B77" s="20">
@@ -24444,7 +24418,7 @@
       <c r="Q77" s="63"/>
       <c r="R77" s="63"/>
       <c r="S77" s="21"/>
-      <c r="V77" s="69"/>
+      <c r="V77" s="73"/>
     </row>
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="22"/>
@@ -24464,7 +24438,7 @@
       <c r="Q78" s="64"/>
       <c r="R78" s="64"/>
       <c r="S78" s="31"/>
-      <c r="V78" s="69"/>
+      <c r="V78" s="73"/>
     </row>
     <row r="79" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B79" s="12"/>
@@ -24476,7 +24450,7 @@
       <c r="H79" s="61"/>
       <c r="I79" s="61"/>
       <c r="J79" s="61"/>
-      <c r="K79" s="74"/>
+      <c r="K79" s="61"/>
       <c r="L79" s="61"/>
       <c r="M79" s="61"/>
       <c r="N79" s="61"/>
@@ -24484,7 +24458,7 @@
       <c r="P79" s="61"/>
       <c r="Q79" s="61"/>
       <c r="R79" s="61"/>
-      <c r="V79" s="69"/>
+      <c r="V79" s="73"/>
     </row>
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="17"/>
@@ -24495,7 +24469,7 @@
       <c r="H80" s="62"/>
       <c r="I80" s="62"/>
       <c r="J80" s="62"/>
-      <c r="K80" s="75"/>
+      <c r="K80" s="62"/>
       <c r="L80" s="62"/>
       <c r="M80" s="62"/>
       <c r="N80" s="62"/>
@@ -24504,7 +24478,7 @@
       <c r="Q80" s="62"/>
       <c r="R80" s="62"/>
       <c r="S80" s="19"/>
-      <c r="V80" s="69"/>
+      <c r="V80" s="73"/>
     </row>
     <row r="81" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B81" s="20">
@@ -24518,7 +24492,7 @@
       <c r="H81" s="63"/>
       <c r="I81" s="63"/>
       <c r="J81" s="63"/>
-      <c r="K81" s="73"/>
+      <c r="K81" s="63"/>
       <c r="L81" s="63"/>
       <c r="M81" s="63"/>
       <c r="N81" s="63"/>
@@ -24527,7 +24501,7 @@
       <c r="Q81" s="63"/>
       <c r="R81" s="63"/>
       <c r="S81" s="21"/>
-      <c r="V81" s="69"/>
+      <c r="V81" s="73"/>
     </row>
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="22"/>
@@ -24538,7 +24512,7 @@
       <c r="H82" s="64"/>
       <c r="I82" s="64"/>
       <c r="J82" s="64"/>
-      <c r="K82" s="76"/>
+      <c r="K82" s="64"/>
       <c r="L82" s="64"/>
       <c r="M82" s="64"/>
       <c r="N82" s="64"/>
@@ -24547,12 +24521,12 @@
       <c r="Q82" s="64"/>
       <c r="R82" s="64"/>
       <c r="S82" s="31"/>
-      <c r="V82" s="70"/>
+      <c r="V82" s="74"/>
     </row>
     <row r="83" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B83" s="12"/>
       <c r="C83" s="34"/>
-      <c r="D83" s="74"/>
+      <c r="D83" s="61"/>
       <c r="E83" s="61"/>
       <c r="F83" s="61"/>
       <c r="G83" s="61"/>
@@ -24571,7 +24545,7 @@
     </row>
     <row r="84" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B84" s="17"/>
-      <c r="D84" s="75"/>
+      <c r="D84" s="62"/>
       <c r="E84" s="62"/>
       <c r="F84" s="62"/>
       <c r="G84" s="62"/>
@@ -24594,7 +24568,7 @@
         <f>B81+1</f>
         <v>21</v>
       </c>
-      <c r="D85" s="73"/>
+      <c r="D85" s="63"/>
       <c r="E85" s="63"/>
       <c r="F85" s="63"/>
       <c r="G85" s="63"/>
@@ -24614,7 +24588,7 @@
     </row>
     <row r="86" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B86" s="22"/>
-      <c r="D86" s="76"/>
+      <c r="D86" s="64"/>
       <c r="E86" s="64"/>
       <c r="F86" s="64"/>
       <c r="G86" s="64"/>
@@ -24805,7 +24779,7 @@
       <c r="E95" s="61"/>
       <c r="F95" s="61"/>
       <c r="G95" s="61"/>
-      <c r="H95" s="74"/>
+      <c r="H95" s="61"/>
       <c r="I95" s="61"/>
       <c r="J95" s="61"/>
       <c r="K95" s="61"/>
@@ -24824,7 +24798,7 @@
       <c r="E96" s="62"/>
       <c r="F96" s="62"/>
       <c r="G96" s="62"/>
-      <c r="H96" s="75"/>
+      <c r="H96" s="62"/>
       <c r="I96" s="62"/>
       <c r="J96" s="62"/>
       <c r="K96" s="62"/>
@@ -24847,7 +24821,7 @@
       <c r="E97" s="63"/>
       <c r="F97" s="63"/>
       <c r="G97" s="63"/>
-      <c r="H97" s="73"/>
+      <c r="H97" s="63"/>
       <c r="I97" s="63"/>
       <c r="J97" s="63"/>
       <c r="K97" s="63"/>
@@ -24867,7 +24841,7 @@
       <c r="E98" s="64"/>
       <c r="F98" s="64"/>
       <c r="G98" s="64"/>
-      <c r="H98" s="76"/>
+      <c r="H98" s="64"/>
       <c r="I98" s="64"/>
       <c r="J98" s="64"/>
       <c r="K98" s="64"/>
@@ -45952,7 +45926,7 @@
         <v>62</v>
       </c>
       <c r="T3" s="16"/>
-      <c r="V3" s="68" t="s">
+      <c r="V3" s="72" t="s">
         <v>1266</v>
       </c>
     </row>
@@ -46000,7 +45974,7 @@
         <v>62</v>
       </c>
       <c r="S4" s="19"/>
-      <c r="V4" s="69"/>
+      <c r="V4" s="73"/>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="20">
@@ -46052,7 +46026,7 @@
         <v>291</v>
       </c>
       <c r="S5" s="21"/>
-      <c r="V5" s="69"/>
+      <c r="V5" s="73"/>
     </row>
     <row r="6" spans="1:22" s="26" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="22"/>
@@ -46099,7 +46073,7 @@
         <v>62</v>
       </c>
       <c r="S6" s="25"/>
-      <c r="V6" s="69"/>
+      <c r="V6" s="73"/>
     </row>
     <row r="7" spans="1:22" s="30" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="27"/>
@@ -46130,7 +46104,7 @@
       <c r="Q7" s="55"/>
       <c r="R7" s="55"/>
       <c r="S7" s="29"/>
-      <c r="V7" s="69"/>
+      <c r="V7" s="73"/>
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="17"/>
@@ -46174,7 +46148,7 @@
         <v>1227</v>
       </c>
       <c r="S8" s="19"/>
-      <c r="V8" s="69"/>
+      <c r="V8" s="73"/>
     </row>
     <row r="9" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="20">
@@ -46228,7 +46202,7 @@
       </c>
       <c r="S9" s="21"/>
       <c r="T9" s="16"/>
-      <c r="V9" s="69"/>
+      <c r="V9" s="73"/>
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="22"/>
@@ -46272,7 +46246,7 @@
         <v>399</v>
       </c>
       <c r="S10" s="31"/>
-      <c r="V10" s="69"/>
+      <c r="V10" s="73"/>
     </row>
     <row r="11" spans="1:22" s="29" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="32"/>
@@ -46296,7 +46270,7 @@
       <c r="P11" s="55"/>
       <c r="Q11" s="55"/>
       <c r="R11" s="55"/>
-      <c r="V11" s="69"/>
+      <c r="V11" s="73"/>
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="17"/>
@@ -46326,7 +46300,7 @@
       <c r="Q12" s="18"/>
       <c r="R12" s="18"/>
       <c r="S12" s="19"/>
-      <c r="V12" s="69"/>
+      <c r="V12" s="73"/>
     </row>
     <row r="13" spans="1:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="20">
@@ -46365,7 +46339,7 @@
       <c r="Q13" s="41"/>
       <c r="R13" s="41"/>
       <c r="S13" s="21"/>
-      <c r="V13" s="69"/>
+      <c r="V13" s="73"/>
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="22"/>
@@ -46395,7 +46369,7 @@
       <c r="Q14" s="24"/>
       <c r="R14" s="24"/>
       <c r="S14" s="31"/>
-      <c r="V14" s="69"/>
+      <c r="V14" s="73"/>
     </row>
     <row r="15" spans="1:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="12"/>
@@ -46415,7 +46389,7 @@
       <c r="P15" s="55"/>
       <c r="Q15" s="55"/>
       <c r="R15" s="55"/>
-      <c r="V15" s="69"/>
+      <c r="V15" s="73"/>
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="17"/>
@@ -46435,7 +46409,7 @@
       <c r="Q16" s="18"/>
       <c r="R16" s="18"/>
       <c r="S16" s="19"/>
-      <c r="V16" s="69"/>
+      <c r="V16" s="73"/>
     </row>
     <row r="17" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="20">
@@ -46460,7 +46434,7 @@
       <c r="Q17" s="41"/>
       <c r="R17" s="41"/>
       <c r="S17" s="21"/>
-      <c r="V17" s="69"/>
+      <c r="V17" s="73"/>
     </row>
     <row r="18" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="22"/>
@@ -46480,7 +46454,7 @@
       <c r="Q18" s="24"/>
       <c r="R18" s="24"/>
       <c r="S18" s="31"/>
-      <c r="V18" s="69"/>
+      <c r="V18" s="73"/>
     </row>
     <row r="19" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="12"/>
@@ -46522,7 +46496,7 @@
       <c r="R19" s="55" t="s">
         <v>1178</v>
       </c>
-      <c r="V19" s="69"/>
+      <c r="V19" s="73"/>
     </row>
     <row r="20" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="17"/>
@@ -46570,7 +46544,7 @@
         <v>1178</v>
       </c>
       <c r="S20" s="19"/>
-      <c r="V20" s="69"/>
+      <c r="V20" s="73"/>
     </row>
     <row r="21" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="20">
@@ -46623,7 +46597,7 @@
         <v>185</v>
       </c>
       <c r="S21" s="21"/>
-      <c r="V21" s="69"/>
+      <c r="V21" s="73"/>
     </row>
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="22"/>
@@ -46671,7 +46645,7 @@
         <v>1323</v>
       </c>
       <c r="S22" s="31"/>
-      <c r="V22" s="69"/>
+      <c r="V22" s="73"/>
     </row>
     <row r="23" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="12"/>
@@ -46691,7 +46665,7 @@
       <c r="P23" s="55"/>
       <c r="Q23" s="55"/>
       <c r="R23" s="55"/>
-      <c r="V23" s="69"/>
+      <c r="V23" s="73"/>
     </row>
     <row r="24" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B24" s="17"/>
@@ -46711,7 +46685,7 @@
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="19"/>
-      <c r="V24" s="69"/>
+      <c r="V24" s="73"/>
     </row>
     <row r="25" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B25" s="20">
@@ -46738,7 +46712,7 @@
       <c r="Q25" s="41"/>
       <c r="R25" s="41"/>
       <c r="S25" s="21"/>
-      <c r="V25" s="69"/>
+      <c r="V25" s="73"/>
     </row>
     <row r="26" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B26" s="22"/>
@@ -46758,7 +46732,7 @@
       <c r="Q26" s="24"/>
       <c r="R26" s="24"/>
       <c r="S26" s="31"/>
-      <c r="V26" s="69"/>
+      <c r="V26" s="73"/>
     </row>
     <row r="27" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B27" s="12"/>
@@ -46782,7 +46756,7 @@
         <f t="shared" ref="U27:U32" si="1" xml:space="preserve"> MID($N$26,4,1)</f>
         <v/>
       </c>
-      <c r="V27" s="69"/>
+      <c r="V27" s="73"/>
     </row>
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="17"/>
@@ -46806,7 +46780,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V28" s="69"/>
+      <c r="V28" s="73"/>
     </row>
     <row r="29" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B29" s="20">
@@ -46835,7 +46809,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V29" s="69"/>
+      <c r="V29" s="73"/>
     </row>
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="22"/>
@@ -46859,7 +46833,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V30" s="69"/>
+      <c r="V30" s="73"/>
     </row>
     <row r="31" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B31" s="12"/>
@@ -46899,7 +46873,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V31" s="69"/>
+      <c r="V31" s="73"/>
     </row>
     <row r="32" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="17"/>
@@ -46949,7 +46923,7 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="V32" s="69"/>
+      <c r="V32" s="73"/>
     </row>
     <row r="33" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B33" s="20">
@@ -47002,7 +46976,7 @@
         <v>164</v>
       </c>
       <c r="S33" s="21"/>
-      <c r="V33" s="69"/>
+      <c r="V33" s="73"/>
     </row>
     <row r="34" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="22"/>
@@ -47048,7 +47022,7 @@
         <v>1320</v>
       </c>
       <c r="S34" s="31"/>
-      <c r="V34" s="69"/>
+      <c r="V34" s="73"/>
     </row>
     <row r="35" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B35" s="12"/>
@@ -47074,7 +47048,7 @@
       <c r="P35" s="55"/>
       <c r="Q35" s="55"/>
       <c r="R35" s="55"/>
-      <c r="V35" s="69"/>
+      <c r="V35" s="73"/>
     </row>
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="17"/>
@@ -47100,7 +47074,7 @@
       <c r="Q36" s="18"/>
       <c r="R36" s="18"/>
       <c r="S36" s="19"/>
-      <c r="V36" s="69"/>
+      <c r="V36" s="73"/>
     </row>
     <row r="37" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B37" s="20">
@@ -47137,7 +47111,7 @@
       <c r="Q37" s="41"/>
       <c r="R37" s="41"/>
       <c r="S37" s="21"/>
-      <c r="V37" s="69"/>
+      <c r="V37" s="73"/>
     </row>
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="22"/>
@@ -47163,7 +47137,7 @@
       <c r="Q38" s="24"/>
       <c r="R38" s="24"/>
       <c r="S38" s="31"/>
-      <c r="V38" s="69"/>
+      <c r="V38" s="73"/>
     </row>
     <row r="39" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B39" s="12"/>
@@ -47183,7 +47157,7 @@
       <c r="P39" s="55"/>
       <c r="Q39" s="55"/>
       <c r="R39" s="55"/>
-      <c r="V39" s="69"/>
+      <c r="V39" s="73"/>
     </row>
     <row r="40" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="17"/>
@@ -47203,7 +47177,7 @@
       <c r="Q40" s="18"/>
       <c r="R40" s="18"/>
       <c r="S40" s="19"/>
-      <c r="V40" s="69"/>
+      <c r="V40" s="73"/>
     </row>
     <row r="41" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B41" s="20">
@@ -47228,7 +47202,7 @@
       <c r="Q41" s="41"/>
       <c r="R41" s="41"/>
       <c r="S41" s="21"/>
-      <c r="V41" s="69"/>
+      <c r="V41" s="73"/>
     </row>
     <row r="42" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="22"/>
@@ -47248,7 +47222,7 @@
       <c r="Q42" s="24"/>
       <c r="R42" s="24"/>
       <c r="S42" s="31"/>
-      <c r="V42" s="69"/>
+      <c r="V42" s="73"/>
     </row>
     <row r="43" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B43" s="12"/>
@@ -47276,7 +47250,7 @@
         <v>1302</v>
       </c>
       <c r="R43" s="55"/>
-      <c r="V43" s="69"/>
+      <c r="V43" s="73"/>
     </row>
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="17"/>
@@ -47322,7 +47296,7 @@
         <v>1293</v>
       </c>
       <c r="S44" s="19"/>
-      <c r="V44" s="69"/>
+      <c r="V44" s="73"/>
     </row>
     <row r="45" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B45" s="20">
@@ -47375,7 +47349,7 @@
         <v>1194</v>
       </c>
       <c r="S45" s="21"/>
-      <c r="V45" s="69"/>
+      <c r="V45" s="73"/>
     </row>
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="22"/>
@@ -47421,7 +47395,7 @@
         <v>1369</v>
       </c>
       <c r="S46" s="31"/>
-      <c r="V46" s="69"/>
+      <c r="V46" s="73"/>
     </row>
     <row r="47" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B47" s="12"/>
@@ -47447,7 +47421,7 @@
       <c r="P47" s="55"/>
       <c r="Q47" s="55"/>
       <c r="R47" s="55"/>
-      <c r="V47" s="69"/>
+      <c r="V47" s="73"/>
     </row>
     <row r="48" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B48" s="17"/>
@@ -47473,7 +47447,7 @@
       <c r="Q48" s="18"/>
       <c r="R48" s="18"/>
       <c r="S48" s="19"/>
-      <c r="V48" s="69"/>
+      <c r="V48" s="73"/>
     </row>
     <row r="49" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B49" s="20">
@@ -47506,7 +47480,7 @@
       <c r="Q49" s="41"/>
       <c r="R49" s="41"/>
       <c r="S49" s="21"/>
-      <c r="V49" s="69"/>
+      <c r="V49" s="73"/>
     </row>
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="22"/>
@@ -47532,7 +47506,7 @@
       <c r="Q50" s="24"/>
       <c r="R50" s="24"/>
       <c r="S50" s="31"/>
-      <c r="V50" s="69"/>
+      <c r="V50" s="73"/>
     </row>
     <row r="51" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B51" s="12"/>
@@ -47552,7 +47526,7 @@
       <c r="P51" s="55"/>
       <c r="Q51" s="55"/>
       <c r="R51" s="55"/>
-      <c r="V51" s="69"/>
+      <c r="V51" s="73"/>
     </row>
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="17"/>
@@ -47572,7 +47546,7 @@
       <c r="Q52" s="18"/>
       <c r="R52" s="18"/>
       <c r="S52" s="19"/>
-      <c r="V52" s="69"/>
+      <c r="V52" s="73"/>
     </row>
     <row r="53" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B53" s="20">
@@ -47597,7 +47571,7 @@
       <c r="Q53" s="41"/>
       <c r="R53" s="41"/>
       <c r="S53" s="21"/>
-      <c r="V53" s="69"/>
+      <c r="V53" s="73"/>
     </row>
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="22"/>
@@ -47617,7 +47591,7 @@
       <c r="Q54" s="24"/>
       <c r="R54" s="24"/>
       <c r="S54" s="31"/>
-      <c r="V54" s="69"/>
+      <c r="V54" s="73"/>
     </row>
     <row r="55" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B55" s="12"/>
@@ -47649,7 +47623,7 @@
       </c>
       <c r="Q55" s="55"/>
       <c r="R55" s="55"/>
-      <c r="V55" s="69"/>
+      <c r="V55" s="73"/>
     </row>
     <row r="56" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="17"/>
@@ -47695,7 +47669,7 @@
         <v>57</v>
       </c>
       <c r="S56" s="19"/>
-      <c r="V56" s="69"/>
+      <c r="V56" s="73"/>
     </row>
     <row r="57" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B57" s="20">
@@ -47748,7 +47722,7 @@
         <v>164</v>
       </c>
       <c r="S57" s="21"/>
-      <c r="V57" s="69"/>
+      <c r="V57" s="73"/>
     </row>
     <row r="58" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="22"/>
@@ -47794,7 +47768,7 @@
         <v>1320</v>
       </c>
       <c r="S58" s="31"/>
-      <c r="V58" s="69"/>
+      <c r="V58" s="73"/>
     </row>
     <row r="59" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B59" s="12"/>
@@ -47816,7 +47790,7 @@
       <c r="P59" s="55"/>
       <c r="Q59" s="55"/>
       <c r="R59" s="55"/>
-      <c r="V59" s="69"/>
+      <c r="V59" s="73"/>
     </row>
     <row r="60" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="17"/>
@@ -47842,7 +47816,7 @@
       <c r="Q60" s="18"/>
       <c r="R60" s="18"/>
       <c r="S60" s="19"/>
-      <c r="V60" s="69"/>
+      <c r="V60" s="73"/>
     </row>
     <row r="61" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B61" s="20">
@@ -47875,7 +47849,7 @@
       <c r="Q61" s="41"/>
       <c r="R61" s="41"/>
       <c r="S61" s="21"/>
-      <c r="V61" s="69"/>
+      <c r="V61" s="73"/>
     </row>
     <row r="62" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B62" s="22"/>
@@ -47901,7 +47875,7 @@
       <c r="Q62" s="24"/>
       <c r="R62" s="24"/>
       <c r="S62" s="31"/>
-      <c r="V62" s="69"/>
+      <c r="V62" s="73"/>
     </row>
     <row r="63" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B63" s="12"/>
@@ -47921,7 +47895,7 @@
       <c r="P63" s="55"/>
       <c r="Q63" s="55"/>
       <c r="R63" s="55"/>
-      <c r="V63" s="69"/>
+      <c r="V63" s="73"/>
     </row>
     <row r="64" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B64" s="17"/>
@@ -47941,7 +47915,7 @@
       <c r="Q64" s="18"/>
       <c r="R64" s="18"/>
       <c r="S64" s="19"/>
-      <c r="V64" s="69"/>
+      <c r="V64" s="73"/>
     </row>
     <row r="65" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B65" s="20">
@@ -47964,7 +47938,7 @@
       <c r="Q65" s="41"/>
       <c r="R65" s="41"/>
       <c r="S65" s="21"/>
-      <c r="V65" s="69"/>
+      <c r="V65" s="73"/>
     </row>
     <row r="66" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B66" s="22"/>
@@ -47984,7 +47958,7 @@
       <c r="Q66" s="24"/>
       <c r="R66" s="24"/>
       <c r="S66" s="31"/>
-      <c r="V66" s="69"/>
+      <c r="V66" s="73"/>
     </row>
     <row r="67" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B67" s="12"/>
@@ -48004,7 +47978,7 @@
       <c r="P67" s="55"/>
       <c r="Q67" s="55"/>
       <c r="R67" s="55"/>
-      <c r="V67" s="69"/>
+      <c r="V67" s="73"/>
     </row>
     <row r="68" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="17"/>
@@ -48024,7 +47998,7 @@
       <c r="Q68" s="18"/>
       <c r="R68" s="18"/>
       <c r="S68" s="19"/>
-      <c r="V68" s="69"/>
+      <c r="V68" s="73"/>
     </row>
     <row r="69" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B69" s="20">
@@ -48047,7 +48021,7 @@
       <c r="Q69" s="41"/>
       <c r="R69" s="41"/>
       <c r="S69" s="21"/>
-      <c r="V69" s="69"/>
+      <c r="V69" s="73"/>
     </row>
     <row r="70" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="22"/>
@@ -48067,7 +48041,7 @@
       <c r="Q70" s="24"/>
       <c r="R70" s="24"/>
       <c r="S70" s="31"/>
-      <c r="V70" s="69"/>
+      <c r="V70" s="73"/>
     </row>
     <row r="71" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B71" s="12"/>
@@ -48087,7 +48061,7 @@
       <c r="P71" s="55"/>
       <c r="Q71" s="55"/>
       <c r="R71" s="55"/>
-      <c r="V71" s="69"/>
+      <c r="V71" s="73"/>
     </row>
     <row r="72" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B72" s="17"/>
@@ -48107,7 +48081,7 @@
       <c r="Q72" s="18"/>
       <c r="R72" s="18"/>
       <c r="S72" s="19"/>
-      <c r="V72" s="69"/>
+      <c r="V72" s="73"/>
     </row>
     <row r="73" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B73" s="20">
@@ -48130,7 +48104,7 @@
       <c r="Q73" s="41"/>
       <c r="R73" s="41"/>
       <c r="S73" s="21"/>
-      <c r="V73" s="69"/>
+      <c r="V73" s="73"/>
     </row>
     <row r="74" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B74" s="22"/>
@@ -48150,7 +48124,7 @@
       <c r="Q74" s="24"/>
       <c r="R74" s="24"/>
       <c r="S74" s="31"/>
-      <c r="V74" s="69"/>
+      <c r="V74" s="73"/>
     </row>
     <row r="75" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B75" s="12"/>
@@ -48170,7 +48144,7 @@
       <c r="P75" s="55"/>
       <c r="Q75" s="55"/>
       <c r="R75" s="55"/>
-      <c r="V75" s="69"/>
+      <c r="V75" s="73"/>
     </row>
     <row r="76" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="17"/>
@@ -48190,7 +48164,7 @@
       <c r="Q76" s="18"/>
       <c r="R76" s="18"/>
       <c r="S76" s="19"/>
-      <c r="V76" s="69"/>
+      <c r="V76" s="73"/>
     </row>
     <row r="77" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B77" s="20">
@@ -48213,7 +48187,7 @@
       <c r="Q77" s="41"/>
       <c r="R77" s="41"/>
       <c r="S77" s="21"/>
-      <c r="V77" s="69"/>
+      <c r="V77" s="73"/>
     </row>
     <row r="78" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="22"/>
@@ -48233,7 +48207,7 @@
       <c r="Q78" s="24"/>
       <c r="R78" s="24"/>
       <c r="S78" s="31"/>
-      <c r="V78" s="69"/>
+      <c r="V78" s="73"/>
     </row>
     <row r="79" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B79" s="12"/>
@@ -48253,7 +48227,7 @@
       <c r="P79" s="55"/>
       <c r="Q79" s="55"/>
       <c r="R79" s="55"/>
-      <c r="V79" s="69"/>
+      <c r="V79" s="73"/>
     </row>
     <row r="80" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="17"/>
@@ -48273,7 +48247,7 @@
       <c r="Q80" s="18"/>
       <c r="R80" s="18"/>
       <c r="S80" s="19"/>
-      <c r="V80" s="69"/>
+      <c r="V80" s="73"/>
     </row>
     <row r="81" spans="2:22" s="6" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B81" s="20">
@@ -48296,7 +48270,7 @@
       <c r="Q81" s="41"/>
       <c r="R81" s="41"/>
       <c r="S81" s="21"/>
-      <c r="V81" s="69"/>
+      <c r="V81" s="73"/>
     </row>
     <row r="82" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="22"/>
@@ -48316,7 +48290,7 @@
       <c r="Q82" s="24"/>
       <c r="R82" s="24"/>
       <c r="S82" s="31"/>
-      <c r="V82" s="70"/>
+      <c r="V82" s="74"/>
     </row>
     <row r="83" spans="2:22" s="35" customFormat="1" ht="60" customHeight="1">
       <c r="B83" s="12"/>
@@ -56308,19 +56282,19 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D3:R3">
-    <cfRule type="expression" dxfId="149" priority="93">
+    <cfRule type="expression" dxfId="149" priority="94">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="148" priority="93">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="148" priority="94">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D7:R7">
-    <cfRule type="expression" dxfId="147" priority="57">
+    <cfRule type="expression" dxfId="147" priority="58">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="146" priority="57">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="146" priority="58">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:R11">
@@ -56332,11 +56306,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="expression" dxfId="143" priority="53">
+    <cfRule type="expression" dxfId="143" priority="54">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="142" priority="53">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="142" priority="54">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:R19">
@@ -56364,35 +56338,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D31:R31">
-    <cfRule type="expression" dxfId="135" priority="45">
+    <cfRule type="expression" dxfId="135" priority="46">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="134" priority="45">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="134" priority="46">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D35:R35">
-    <cfRule type="expression" dxfId="133" priority="43">
+    <cfRule type="expression" dxfId="133" priority="44">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="132" priority="43">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="132" priority="44">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D39:R39">
-    <cfRule type="expression" dxfId="131" priority="41">
+    <cfRule type="expression" dxfId="131" priority="42">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="130" priority="41">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="130" priority="42">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43:R43">
-    <cfRule type="expression" dxfId="129" priority="39">
+    <cfRule type="expression" dxfId="129" priority="40">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="128" priority="39">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="128" priority="40">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D47:R47">
@@ -56428,11 +56402,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D63:R63">
-    <cfRule type="expression" dxfId="119" priority="29">
+    <cfRule type="expression" dxfId="119" priority="30">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="118" priority="29">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="118" priority="30">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:R67">
@@ -56452,19 +56426,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D75:R75">
-    <cfRule type="expression" dxfId="113" priority="23">
+    <cfRule type="expression" dxfId="113" priority="24">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="112" priority="23">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="112" priority="24">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D79:R79">
-    <cfRule type="expression" dxfId="111" priority="21">
+    <cfRule type="expression" dxfId="111" priority="22">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="110" priority="21">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="110" priority="22">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:R83">
@@ -56492,11 +56466,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D95:R95">
-    <cfRule type="expression" dxfId="103" priority="13">
+    <cfRule type="expression" dxfId="103" priority="14">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="102" priority="13">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="14">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D99:R99">
@@ -56508,19 +56482,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D103:R103">
-    <cfRule type="expression" dxfId="99" priority="9">
+    <cfRule type="expression" dxfId="99" priority="10">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="98" priority="9">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="98" priority="10">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D107:R107">
-    <cfRule type="expression" dxfId="97" priority="7">
+    <cfRule type="expression" dxfId="97" priority="8">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="96" priority="7">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="96" priority="8">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D111:R111">
@@ -56548,43 +56522,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D123:R123 D127:R127 D131:R131 D135:R135 D139:R139 D143:R143 D147:R147 D151:R151 D155:R155 D159:R159 D163:R163">
-    <cfRule type="expression" dxfId="89" priority="101">
+    <cfRule type="expression" dxfId="89" priority="102">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="88" priority="101">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="102">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D167:R167 D171:R171 D175:R175 D179:R179 D183:R183 D187:R187 D191:R191 D195:R195 D199:R199">
-    <cfRule type="expression" dxfId="87" priority="99">
+    <cfRule type="expression" dxfId="87" priority="100">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="99">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="86" priority="100">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D203:R203">
-    <cfRule type="expression" dxfId="85" priority="97">
+    <cfRule type="expression" dxfId="85" priority="98">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="97">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="98">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D207:R207 D211:R211 D215:R215 D219:R219 D223:R223 D227:R227 D231:R231 D235:R235 D239:R239">
-    <cfRule type="expression" dxfId="83" priority="95">
+    <cfRule type="expression" dxfId="83" priority="96">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="95">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="96">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D243:R243">
-    <cfRule type="expression" dxfId="81" priority="91">
+    <cfRule type="expression" dxfId="81" priority="92">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="91">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="92">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D247:R247 D251:R251 D255:R255 D259:R259 D263:R263 D267:R267 D271:R271 D275:R275 D279:R279">
@@ -56652,43 +56626,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D375:R375">
-    <cfRule type="expression" dxfId="63" priority="73">
+    <cfRule type="expression" dxfId="63" priority="74">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="73">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="74">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D379:R379 D383:R383 D387:R387 D391:R391 D395:R395 D399:R399 D403:R403 D407:R407 D411:R411">
-    <cfRule type="expression" dxfId="61" priority="71">
+    <cfRule type="expression" dxfId="61" priority="72">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="71">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="72">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D415:R415">
-    <cfRule type="expression" dxfId="59" priority="69">
+    <cfRule type="expression" dxfId="59" priority="70">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="69">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="70">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D419:R419">
-    <cfRule type="expression" dxfId="57" priority="67">
+    <cfRule type="expression" dxfId="57" priority="68">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="67">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="68">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D423:R423 D427:R427 D431:R431 D435:R435 D439:R439 D443:R443 D447:R447 D451:R451 D455:R455">
-    <cfRule type="expression" dxfId="55" priority="65">
+    <cfRule type="expression" dxfId="55" priority="66">
+      <formula>"'= TRUE(顯示注音輸入)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="65">
       <formula>顯示注音輸入</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="66">
-      <formula>"'= TRUE(顯示注音輸入)"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D459:R459">
